--- a/VerveStacks_POL_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24DA5BE2-8552-44BD-BE37-DC2C1F22AA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C79DD69F-86F9-453E-8FBB-66ABFB5E793C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="499">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -852,16 +852,106 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_016</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_014</t>
@@ -876,102 +966,12 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_012</t>
   </si>
   <si>
@@ -984,64 +984,115 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w111615226-220_POL,e_w255314292_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>e_w86494356-400_POL,e_w39428977-400_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL75-220_POL,e_w293484891-220_POL,e_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
     <t>e_w293484891-220_POL</t>
   </si>
   <si>
+    <t>e_PL17-400_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>e_w29115701-220_POL,e_w111615226-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255314292_POL</t>
+  </si>
+  <si>
+    <t>e_w39428977-400_POL,e_LT1-400_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL,e_PL75-220_POL,e_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>e_w293484891-220_POL,e_w86494356-400_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL,e_PL75-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL,e_w29115701-220_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
     <t>e_PL75-220_POL,e_w133537926-220_POL,e_w191035265-220_POL</t>
   </si>
   <si>
     <t>e_w29115701-220_POL,e_w293484891-220_POL</t>
   </si>
   <si>
-    <t>e_PL75-220_POL,e_w255277953-400_POL,e_w293484891-220_POL,e_w191035265-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
     <t>e_w303870256-400_POL,e_PL17-400_POL</t>
   </si>
   <si>
-    <t>e_PL17-400_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL,e_PL75-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL,e_w29115701-220_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>e_w29115701-220_POL,e_w111615226-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL,e_PL17-400_POL,e_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>e_w86494356-400_POL,e_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>e_w39428977-400_POL,e_LT1-400_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL,e_w255277953-400_POL,e_w293484891-220_POL</t>
-  </si>
-  <si>
-    <t>e_w293484891-220_POL,e_w86494356-400_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL,e_w255314292_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191035265-220_POL,e_PL17-400_POL</t>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_018</t>
@@ -1062,12 +1113,6 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_009</t>
   </si>
   <si>
@@ -1092,36 +1137,6 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_015</t>
   </si>
   <si>
@@ -1134,24 +1149,6 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_012</t>
   </si>
   <si>
@@ -1164,12 +1161,54 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_w39428977-400_POL,e_LT1-400_POL,e_w255314292_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_w293484891-220_POL,e_w191035265-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_w133537926-220_POL,e_w293484891-220_POL,e_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL,e_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_w29115701-220_POL,e_w303870256-400_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>e_w111615226-220_POL,e_PL75-220_POL,e_w255277953-400_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
@@ -1179,12 +1218,6 @@
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_w133537926-220_POL,e_w293484891-220_POL,e_w191035265-220_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
@@ -1197,28 +1230,7 @@
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>e_PL75-220_POL,e_w255277953-400_POL,e_w293484891-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_w39428977-400_POL,e_LT1-400_POL,e_w255314292_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_w293484891-220_POL,e_w191035265-220_POL,e_w29115701-220_POL</t>
+    <t>e_PL75-220_POL,e_w293484891-220_POL</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
@@ -1230,27 +1242,6 @@
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>e_w166838338-400_POL,e_w191035265-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL,e_w293484891-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_w29115701-220_POL,e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL,e_w166838338-400_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
@@ -1263,22 +1254,46 @@
     <t>e_w29115701-220_POL,e_w293484891-220_POL,e_PL17-400_POL</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_008</t>
@@ -1293,46 +1308,37 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_w255314292_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1344,22 +1350,7 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
     <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -3566,7 +3557,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -6367,7 +6358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3465E6F1-6DBC-45E0-B9AA-749F08109D3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B4B8B25-8834-468D-8B14-A30825D2C76B}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6605,25 +6596,25 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99839233674974392</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB11">
-        <v>29.473826254695162</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
       </c>
       <c r="AE11" t="s">
+        <v>304</v>
+      </c>
+      <c r="AF11" t="s">
         <v>305</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>306</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6638,28 +6629,28 @@
         <v>176</v>
       </c>
       <c r="AL11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AM11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN11" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="AO11">
-        <v>0.99622969699231045</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP11">
-        <v>69.122221807641537</v>
+        <v>36.244421623259619</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
       </c>
       <c r="AS11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AT11" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6674,19 +6665,19 @@
         <v>176</v>
       </c>
       <c r="AZ11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="BA11" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="BB11" t="s">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="BC11">
-        <v>0.99603343715055259</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD11">
-        <v>72.720318906536249</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6751,25 +6742,25 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99801094175818605</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB12">
-        <v>36.466067766588218</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
       </c>
       <c r="AE12" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF12" t="s">
         <v>307</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>308</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -6784,28 +6775,28 @@
         <v>176</v>
       </c>
       <c r="AL12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AM12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AN12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AO12">
-        <v>0.99845079995590791</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP12">
-        <v>28.402000808355538</v>
+        <v>52.367530010463909</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
       </c>
       <c r="AS12" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AT12" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -6820,19 +6811,19 @@
         <v>176</v>
       </c>
       <c r="AZ12" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="BA12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="BB12" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BC12">
-        <v>0.9932866968373224</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD12">
-        <v>123.07722464908932</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6897,25 +6888,25 @@
         <v>247</v>
       </c>
       <c r="Y13" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="Z13" t="s">
         <v>287</v>
       </c>
       <c r="AA13">
-        <v>0.99909366739195871</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB13">
-        <v>16.616097814091063</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD13" t="s">
         <v>240</v>
       </c>
       <c r="AE13" t="s">
+        <v>308</v>
+      </c>
+      <c r="AF13" t="s">
         <v>309</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>310</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -6930,28 +6921,28 @@
         <v>176</v>
       </c>
       <c r="AL13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AM13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AN13" t="s">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="AO13">
-        <v>0.9963019969989696</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP13">
-        <v>67.796721685557472</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
       </c>
       <c r="AS13" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AT13" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -6966,19 +6957,19 @@
         <v>176</v>
       </c>
       <c r="AZ13" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BA13" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="BB13" t="s">
-        <v>400</v>
+        <v>294</v>
       </c>
       <c r="BC13">
-        <v>0.99644388872049838</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD13">
-        <v>65.195373457529499</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7058,10 +7049,10 @@
         <v>240</v>
       </c>
       <c r="AE14" t="s">
+        <v>310</v>
+      </c>
+      <c r="AF14" t="s">
         <v>311</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>312</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -7076,28 +7067,28 @@
         <v>176</v>
       </c>
       <c r="AL14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AM14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN14" t="s">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="AO14">
-        <v>0.99873239758997023</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP14">
-        <v>23.239377517213022</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
       </c>
       <c r="AS14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AT14" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7112,19 +7103,19 @@
         <v>176</v>
       </c>
       <c r="AZ14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="BA14" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="BB14" t="s">
-        <v>403</v>
+        <v>294</v>
       </c>
       <c r="BC14">
-        <v>0.99383395234396599</v>
+        <v>0.99609037037675463</v>
       </c>
       <c r="BD14">
-        <v>113.04420702728957</v>
+        <v>71.676543092831025</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7204,10 +7195,10 @@
         <v>240</v>
       </c>
       <c r="AE15" t="s">
+        <v>312</v>
+      </c>
+      <c r="AF15" t="s">
         <v>313</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>314</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7222,28 +7213,28 @@
         <v>176</v>
       </c>
       <c r="AL15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AM15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AN15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AO15">
-        <v>0.99635146162488653</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP15">
-        <v>66.889870210414614</v>
+        <v>31.794264857351436</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
       </c>
       <c r="AS15" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AT15" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7258,19 +7249,19 @@
         <v>176</v>
       </c>
       <c r="AZ15" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="BA15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="BB15" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BC15">
-        <v>0.99564789206089888</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD15">
-        <v>79.788645550187297</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7335,25 +7326,25 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99692898913090644</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB16">
-        <v>56.301865933381954</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
       </c>
       <c r="AE16" t="s">
+        <v>314</v>
+      </c>
+      <c r="AF16" t="s">
         <v>315</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>316</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7368,28 +7359,28 @@
         <v>176</v>
       </c>
       <c r="AL16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AM16" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AN16" t="s">
-        <v>297</v>
+        <v>352</v>
       </c>
       <c r="AO16">
-        <v>0.99586212495478665</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP16">
-        <v>75.861042495577635</v>
+        <v>23.583853720120768</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
       </c>
       <c r="AS16" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AT16" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7404,19 +7395,19 @@
         <v>176</v>
       </c>
       <c r="AZ16" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="BA16" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB16" t="s">
-        <v>303</v>
+        <v>402</v>
       </c>
       <c r="BC16">
-        <v>0.99609037037675463</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD16">
-        <v>71.676543092831025</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7496,10 +7487,10 @@
         <v>240</v>
       </c>
       <c r="AE17" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF17" t="s">
         <v>317</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>318</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7514,28 +7505,28 @@
         <v>176</v>
       </c>
       <c r="AL17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AM17" t="s">
+        <v>353</v>
+      </c>
+      <c r="AN17" t="s">
         <v>354</v>
       </c>
-      <c r="AN17" t="s">
-        <v>302</v>
-      </c>
       <c r="AO17">
-        <v>0.99730422320290779</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP17">
-        <v>49.422574613357185</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
       </c>
       <c r="AS17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AT17" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7550,19 +7541,19 @@
         <v>176</v>
       </c>
       <c r="AZ17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="BA17" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="BB17" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BC17">
-        <v>0.99353710926584593</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD17">
-        <v>118.48633012615811</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7627,25 +7618,25 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.99733507264559695</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB18">
-        <v>48.857001497390002</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
       </c>
       <c r="AE18" t="s">
+        <v>318</v>
+      </c>
+      <c r="AF18" t="s">
         <v>319</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>320</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -7660,7 +7651,7 @@
         <v>176</v>
       </c>
       <c r="AL18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AM18" t="s">
         <v>355</v>
@@ -7669,19 +7660,19 @@
         <v>356</v>
       </c>
       <c r="AO18">
-        <v>0.99805709209211746</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP18">
-        <v>35.619978311179104</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
       </c>
       <c r="AS18" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AT18" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7696,19 +7687,19 @@
         <v>176</v>
       </c>
       <c r="AZ18" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="BA18" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="BB18" t="s">
-        <v>303</v>
+        <v>405</v>
       </c>
       <c r="BC18">
-        <v>0.99399718012600935</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD18">
-        <v>110.05169768982766</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7773,25 +7764,25 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.99583365539385327</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB19">
-        <v>76.382984446022675</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
       </c>
       <c r="AE19" t="s">
+        <v>320</v>
+      </c>
+      <c r="AF19" t="s">
         <v>321</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>322</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -7806,28 +7797,28 @@
         <v>176</v>
       </c>
       <c r="AL19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AM19" t="s">
         <v>357</v>
       </c>
       <c r="AN19" t="s">
-        <v>296</v>
+        <v>358</v>
       </c>
       <c r="AO19">
-        <v>0.99653588726932718</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP19">
-        <v>63.508733395668145</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
       </c>
       <c r="AS19" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AT19" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -7842,19 +7833,19 @@
         <v>176</v>
       </c>
       <c r="AZ19" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="BA19" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BB19" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="BC19">
-        <v>0.99255696761939116</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD19">
-        <v>136.4555936444961</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7919,25 +7910,25 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99875154162789404</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB20">
-        <v>22.888403488609324</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
       </c>
       <c r="AE20" t="s">
+        <v>322</v>
+      </c>
+      <c r="AF20" t="s">
         <v>323</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>324</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -7952,28 +7943,28 @@
         <v>176</v>
       </c>
       <c r="AL20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AM20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN20" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AO20">
-        <v>0.99802303154782224</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP20">
-        <v>36.244421623259619</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
       </c>
       <c r="AS20" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AT20" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -7988,19 +7979,19 @@
         <v>176</v>
       </c>
       <c r="AZ20" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="BA20" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="BB20" t="s">
-        <v>400</v>
+        <v>294</v>
       </c>
       <c r="BC20">
-        <v>0.99615776238359954</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD20">
-        <v>70.441022967342263</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8065,25 +8056,25 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99511607748745434</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB21">
-        <v>89.538579396670116</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
       </c>
       <c r="AE21" t="s">
+        <v>324</v>
+      </c>
+      <c r="AF21" t="s">
         <v>325</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>326</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8098,19 +8089,19 @@
         <v>176</v>
       </c>
       <c r="AL21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AM21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO21">
-        <v>0.99714358927215652</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP21">
-        <v>52.367530010463909</v>
+        <v>28.402000808355538</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8175,25 +8166,25 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99648087644372252</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB22">
-        <v>64.517265198419722</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
       </c>
       <c r="AE22" t="s">
+        <v>326</v>
+      </c>
+      <c r="AF22" t="s">
         <v>327</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>328</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8208,19 +8199,19 @@
         <v>176</v>
       </c>
       <c r="AL22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM22" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN22" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO22">
-        <v>0.99826576737141715</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP22">
-        <v>31.794264857351436</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8285,25 +8276,25 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99621535905375425</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB23">
-        <v>69.385084014505708</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
       </c>
       <c r="AE23" t="s">
+        <v>328</v>
+      </c>
+      <c r="AF23" t="s">
         <v>329</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>330</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8318,19 +8309,19 @@
         <v>176</v>
       </c>
       <c r="AL23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AM23" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN23" t="s">
-        <v>363</v>
+        <v>286</v>
       </c>
       <c r="AO23">
-        <v>0.99871360797890252</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP23">
-        <v>23.583853720120768</v>
+        <v>66.889870210414614</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8395,25 +8386,25 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99738245649758195</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB24">
-        <v>47.988297544331637</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
       </c>
       <c r="AE24" t="s">
+        <v>330</v>
+      </c>
+      <c r="AF24" t="s">
         <v>331</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>332</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8428,19 +8419,19 @@
         <v>176</v>
       </c>
       <c r="AL24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AM24" t="s">
         <v>364</v>
       </c>
       <c r="AN24" t="s">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="AO24">
-        <v>0.99641308487583879</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP24">
-        <v>65.760110609622657</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8505,25 +8496,25 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99812712894455979</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB25">
-        <v>34.335969349736395</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
       </c>
       <c r="AE25" t="s">
+        <v>332</v>
+      </c>
+      <c r="AF25" t="s">
         <v>333</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>334</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -8538,19 +8529,19 @@
         <v>176</v>
       </c>
       <c r="AL25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AM25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AN25" t="s">
-        <v>367</v>
+        <v>285</v>
       </c>
       <c r="AO25">
-        <v>0.99449756685866841</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP25">
-        <v>100.87794092441324</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8615,25 +8606,25 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99834158364926728</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB26">
-        <v>30.404299763434018</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
       </c>
       <c r="AE26" t="s">
+        <v>334</v>
+      </c>
+      <c r="AF26" t="s">
         <v>335</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>336</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -8648,19 +8639,19 @@
         <v>176</v>
       </c>
       <c r="AL26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AN26" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AO26">
-        <v>0.99883902037019667</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP26">
-        <v>21.284626546395259</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8725,25 +8716,25 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.9987403722896917</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB27">
-        <v>23.093174688985375</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
       </c>
       <c r="AE27" t="s">
+        <v>336</v>
+      </c>
+      <c r="AF27" t="s">
         <v>337</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>338</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -8758,19 +8749,19 @@
         <v>176</v>
       </c>
       <c r="AL27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AM27" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN27" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO27">
-        <v>0.99521984547821263</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP27">
-        <v>87.636166232768815</v>
+        <v>65.760110609622657</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8835,25 +8826,25 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99729953359766199</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB28">
-        <v>49.508550709529651</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
       </c>
       <c r="AE28" t="s">
+        <v>338</v>
+      </c>
+      <c r="AF28" t="s">
         <v>339</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>340</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -8868,19 +8859,19 @@
         <v>176</v>
       </c>
       <c r="AL28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AM28" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AN28" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="AO28">
-        <v>0.99776911581804295</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP28">
-        <v>40.899543335879912</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8945,25 +8936,25 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Z29" t="s">
         <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99763459325217896</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB29">
-        <v>43.365790376719588</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
       </c>
       <c r="AE29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AF29" t="s">
         <v>341</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>342</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -8978,13 +8969,13 @@
         <v>176</v>
       </c>
       <c r="AL29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AM29" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AN29" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AO29">
         <v>0.99749126227646956</v>
@@ -9058,7 +9049,7 @@
         <v>230</v>
       </c>
       <c r="Z30" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="AA30">
         <v>0.99505524223378883</v>
@@ -9070,10 +9061,10 @@
         <v>240</v>
       </c>
       <c r="AE30" t="s">
+        <v>342</v>
+      </c>
+      <c r="AF30" t="s">
         <v>343</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>344</v>
       </c>
       <c r="AG30" t="s">
         <v>10</v>
@@ -9088,13 +9079,13 @@
         <v>176</v>
       </c>
       <c r="AL30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AM30" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AN30" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AO30">
         <v>0.99807543246352515</v>
@@ -9109,7 +9100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1F542D-6EDB-4FC9-91B9-B3303803515C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{655A367F-FF33-4CF0-8E13-1C1B40256B49}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9200,10 +9191,10 @@
         <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -9218,10 +9209,10 @@
         <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="K11" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -9233,10 +9224,10 @@
         <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="Q11" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -9251,10 +9242,10 @@
         <v>176</v>
       </c>
       <c r="W11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="X11" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -9268,10 +9259,10 @@
         <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D12" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -9286,10 +9277,10 @@
         <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="K12" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -9301,10 +9292,10 @@
         <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="Q12" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -9319,10 +9310,10 @@
         <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="X12" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -9336,10 +9327,10 @@
         <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D13" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -9354,10 +9345,10 @@
         <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="K13" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -9369,10 +9360,10 @@
         <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="Q13" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -9387,10 +9378,10 @@
         <v>176</v>
       </c>
       <c r="W13" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="X13" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -9404,10 +9395,10 @@
         <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D14" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -9422,10 +9413,10 @@
         <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="K14" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -9437,10 +9428,10 @@
         <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q14" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -9455,10 +9446,10 @@
         <v>176</v>
       </c>
       <c r="W14" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="X14" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -9472,10 +9463,10 @@
         <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D15" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -9490,10 +9481,10 @@
         <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="K15" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -9505,10 +9496,10 @@
         <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="Q15" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -9523,10 +9514,10 @@
         <v>176</v>
       </c>
       <c r="W15" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="X15" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -9540,10 +9531,10 @@
         <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D16" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -9558,10 +9549,10 @@
         <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K16" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -9573,10 +9564,10 @@
         <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="Q16" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -9591,10 +9582,10 @@
         <v>176</v>
       </c>
       <c r="W16" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="X16" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -9608,10 +9599,10 @@
         <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D17" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -9626,10 +9617,10 @@
         <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="K17" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -9641,10 +9632,10 @@
         <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Q17" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -9659,7 +9650,7 @@
         <v>176</v>
       </c>
       <c r="W17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="X17" t="s">
         <v>398</v>
@@ -9676,10 +9667,10 @@
         <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D18" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -9694,10 +9685,10 @@
         <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="K18" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -9709,10 +9700,10 @@
         <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="Q18" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -9727,10 +9718,10 @@
         <v>176</v>
       </c>
       <c r="W18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="X18" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -9744,10 +9735,10 @@
         <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D19" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -9762,10 +9753,10 @@
         <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="K19" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -9777,10 +9768,10 @@
         <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="Q19" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -9795,7 +9786,7 @@
         <v>176</v>
       </c>
       <c r="W19" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X19" t="s">
         <v>407</v>
@@ -9812,10 +9803,10 @@
         <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D20" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -9830,10 +9821,10 @@
         <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="K20" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -9845,10 +9836,10 @@
         <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="Q20" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -9863,10 +9854,10 @@
         <v>176</v>
       </c>
       <c r="W20" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="X20" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9880,10 +9871,10 @@
         <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D21" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -9898,10 +9889,10 @@
         <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K21" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -9915,10 +9906,10 @@
         <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D22" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -9933,10 +9924,10 @@
         <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="K22" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -9950,10 +9941,10 @@
         <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D23" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -9968,10 +9959,10 @@
         <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="K23" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -9985,10 +9976,10 @@
         <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D24" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -10003,10 +9994,10 @@
         <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="K24" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10020,10 +10011,10 @@
         <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D25" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -10038,10 +10029,10 @@
         <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="K25" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10055,10 +10046,10 @@
         <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D26" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -10073,10 +10064,10 @@
         <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="K26" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10090,10 +10081,10 @@
         <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D27" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -10108,10 +10099,10 @@
         <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="K27" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10125,10 +10116,10 @@
         <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D28" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -10143,10 +10134,10 @@
         <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K28" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10160,10 +10151,10 @@
         <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D29" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -10178,10 +10169,10 @@
         <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="K29" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -10195,10 +10186,10 @@
         <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D30" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -10213,10 +10204,10 @@
         <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K30" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -10231,7 +10222,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C14332-8FA1-42CC-A703-95735E90EC64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9191BB0D-3271-4440-83E4-A7FCFCB3136A}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10298,7 +10289,7 @@
     </row>
     <row r="11" spans="2:19">
       <c r="B11" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
@@ -10316,13 +10307,13 @@
         <v>1000</v>
       </c>
       <c r="K11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M11" t="s">
         <v>172</v>
       </c>
       <c r="N11" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P11" t="s">
         <v>10</v>
@@ -10334,12 +10325,12 @@
         <v>244</v>
       </c>
       <c r="S11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="12" spans="2:19">
       <c r="B12" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
@@ -10357,13 +10348,13 @@
         <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M12" t="s">
         <v>172</v>
       </c>
       <c r="N12" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="P12" t="s">
         <v>10</v>
@@ -10375,12 +10366,12 @@
         <v>244</v>
       </c>
       <c r="S12" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="2:19">
       <c r="B13" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
@@ -10398,13 +10389,13 @@
         <v>0.497</v>
       </c>
       <c r="K13" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M13" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="N13" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="P13" t="s">
         <v>10</v>
@@ -10416,12 +10407,12 @@
         <v>244</v>
       </c>
       <c r="S13" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" spans="2:19">
       <c r="B14" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
@@ -10445,7 +10436,7 @@
         <v>172</v>
       </c>
       <c r="N14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="P14" t="s">
         <v>10</v>
@@ -10457,12 +10448,12 @@
         <v>244</v>
       </c>
       <c r="S14" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="2:19">
       <c r="B15" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -10489,13 +10480,13 @@
         <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="M15" t="s">
         <v>172</v>
       </c>
       <c r="N15" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P15" t="s">
         <v>10</v>
@@ -10507,12 +10498,12 @@
         <v>244</v>
       </c>
       <c r="S15" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="2:19">
       <c r="B16" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -10539,13 +10530,13 @@
         <v>3</v>
       </c>
       <c r="K16" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M16" t="s">
         <v>172</v>
       </c>
       <c r="N16" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="P16" t="s">
         <v>10</v>
@@ -10557,12 +10548,12 @@
         <v>244</v>
       </c>
       <c r="S16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="2:19">
       <c r="B17" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -10580,13 +10571,13 @@
         <v>500</v>
       </c>
       <c r="K17" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M17" t="s">
         <v>172</v>
       </c>
       <c r="N17" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="P17" t="s">
         <v>10</v>
@@ -10598,12 +10589,12 @@
         <v>244</v>
       </c>
       <c r="S17" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" spans="2:19">
       <c r="B18" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C18" t="s">
         <v>33</v>
@@ -10621,13 +10612,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M18" t="s">
         <v>172</v>
       </c>
       <c r="N18" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P18" t="s">
         <v>10</v>
@@ -10639,12 +10630,12 @@
         <v>244</v>
       </c>
       <c r="S18" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" spans="2:19">
       <c r="B19" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -10662,13 +10653,13 @@
         <v>1.9279999999999999</v>
       </c>
       <c r="K19" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M19" t="s">
         <v>172</v>
       </c>
       <c r="N19" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="P19" t="s">
         <v>10</v>
@@ -10680,12 +10671,12 @@
         <v>244</v>
       </c>
       <c r="S19" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="2:19">
       <c r="B20" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
@@ -10709,7 +10700,7 @@
         <v>172</v>
       </c>
       <c r="N20" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="P20" t="s">
         <v>10</v>
@@ -10721,12 +10712,12 @@
         <v>244</v>
       </c>
       <c r="S20" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="2:19">
       <c r="B21" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -10753,13 +10744,13 @@
         <v>30</v>
       </c>
       <c r="K21" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="M21" t="s">
         <v>172</v>
       </c>
       <c r="N21" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="P21" t="s">
         <v>10</v>
@@ -10771,12 +10762,12 @@
         <v>244</v>
       </c>
       <c r="S21" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -10803,13 +10794,13 @@
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M22" t="s">
         <v>172</v>
       </c>
       <c r="N22" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="P22" t="s">
         <v>10</v>
@@ -10821,18 +10812,18 @@
         <v>244</v>
       </c>
       <c r="S22" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="2:19">
       <c r="B23" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E23">
         <v>1300</v>
@@ -10844,13 +10835,13 @@
         <v>1300</v>
       </c>
       <c r="K23" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M23" t="s">
         <v>172</v>
       </c>
       <c r="N23" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="P23" t="s">
         <v>10</v>
@@ -10862,18 +10853,18 @@
         <v>244</v>
       </c>
       <c r="S23" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E24">
         <v>40</v>
@@ -10885,13 +10876,13 @@
         <v>40</v>
       </c>
       <c r="K24" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M24" t="s">
         <v>172</v>
       </c>
       <c r="N24" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="P24" t="s">
         <v>10</v>
@@ -10903,18 +10894,18 @@
         <v>244</v>
       </c>
       <c r="S24" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="2:19">
       <c r="B25" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E25">
         <v>0.69399999999999995</v>
@@ -10926,13 +10917,13 @@
         <v>0.69399999999999995</v>
       </c>
       <c r="K25" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M25" t="s">
         <v>172</v>
       </c>
       <c r="N25" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="P25" t="s">
         <v>10</v>
@@ -10944,18 +10935,18 @@
         <v>244</v>
       </c>
       <c r="S25" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="26" spans="2:19">
       <c r="B26" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E26">
         <v>0.53300000000000003</v>
@@ -10973,7 +10964,7 @@
         <v>172</v>
       </c>
       <c r="N26" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="P26" t="s">
         <v>10</v>
@@ -10985,18 +10976,18 @@
         <v>244</v>
       </c>
       <c r="S26" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" spans="2:19">
       <c r="B27" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C27" t="s">
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E27">
         <v>25</v>
@@ -11017,13 +11008,13 @@
         <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="M27" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="N27" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="P27" t="s">
         <v>10</v>
@@ -11035,18 +11026,18 @@
         <v>244</v>
       </c>
       <c r="S27" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="2:19">
       <c r="B28" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -11067,13 +11058,13 @@
         <v>3</v>
       </c>
       <c r="K28" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M28" t="s">
         <v>172</v>
       </c>
       <c r="N28" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="P28" t="s">
         <v>10</v>
@@ -11085,18 +11076,18 @@
         <v>244</v>
       </c>
       <c r="S28" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="29" spans="2:19">
       <c r="B29" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C29" t="s">
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E29">
         <v>0.35389999999999999</v>
@@ -11117,13 +11108,13 @@
         <v>0.35389999999999999</v>
       </c>
       <c r="K29" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M29" t="s">
         <v>172</v>
       </c>
       <c r="N29" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="P29" t="s">
         <v>10</v>
@@ -11135,12 +11126,12 @@
         <v>244</v>
       </c>
       <c r="S29" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="30" spans="2:19">
       <c r="B30" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -11158,12 +11149,12 @@
         <v>2500</v>
       </c>
       <c r="K30" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -11181,12 +11172,12 @@
         <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -11204,12 +11195,12 @@
         <v>0.83299999999999996</v>
       </c>
       <c r="K32" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="33" spans="2:11">
       <c r="B33" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C33" t="s">
         <v>33</v>
@@ -11232,7 +11223,7 @@
     </row>
     <row r="34" spans="2:11">
       <c r="B34" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C34" t="s">
         <v>33</v>
@@ -11259,12 +11250,12 @@
         <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="B35" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C35" t="s">
         <v>33</v>
@@ -11291,18 +11282,18 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="B36" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C36" t="s">
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E36">
         <v>3100</v>
@@ -11314,18 +11305,18 @@
         <v>2500</v>
       </c>
       <c r="K36" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="B37" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C37" t="s">
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E37">
         <v>80</v>
@@ -11337,18 +11328,18 @@
         <v>60</v>
       </c>
       <c r="K37" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="B38" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E38">
         <v>1.35</v>
@@ -11360,18 +11351,18 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="K38" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="B39" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E39">
         <v>0.51</v>
@@ -11388,13 +11379,13 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E40">
         <v>30</v>
@@ -11415,18 +11406,18 @@
         <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41" spans="2:11">
       <c r="B41" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C41" t="s">
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -11447,12 +11438,12 @@
         <v>4</v>
       </c>
       <c r="K41" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="42" spans="2:11">
       <c r="B42" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -11470,12 +11461,12 @@
         <v>1700</v>
       </c>
       <c r="K42" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43" spans="2:11">
       <c r="B43" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -11493,12 +11484,12 @@
         <v>45</v>
       </c>
       <c r="K43" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44" spans="2:11">
       <c r="B44" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
@@ -11516,12 +11507,12 @@
         <v>2.3610000000000002</v>
       </c>
       <c r="K44" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="2:11">
       <c r="B45" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
@@ -11544,7 +11535,7 @@
     </row>
     <row r="46" spans="2:11">
       <c r="B46" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
@@ -11571,12 +11562,12 @@
         <v>40</v>
       </c>
       <c r="K46" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="47" spans="2:11">
       <c r="B47" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -11603,12 +11594,12 @@
         <v>4</v>
       </c>
       <c r="K47" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="48" spans="2:11">
       <c r="B48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -11626,12 +11617,12 @@
         <v>2000</v>
       </c>
       <c r="K48" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="49" spans="2:11">
       <c r="B49" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -11649,12 +11640,12 @@
         <v>60</v>
       </c>
       <c r="K49" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50" spans="2:11">
       <c r="B50" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C50" t="s">
         <v>32</v>
@@ -11672,12 +11663,12 @@
         <v>2.3170000000000002</v>
       </c>
       <c r="K50" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="51" spans="2:11">
       <c r="B51" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C51" t="s">
         <v>32</v>
@@ -11700,7 +11691,7 @@
     </row>
     <row r="52" spans="2:11">
       <c r="B52" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C52" t="s">
         <v>32</v>
@@ -11727,12 +11718,12 @@
         <v>40</v>
       </c>
       <c r="K52" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="53" spans="2:11">
       <c r="B53" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C53" t="s">
         <v>32</v>
@@ -11759,12 +11750,12 @@
         <v>4</v>
       </c>
       <c r="K53" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="54" spans="2:11">
       <c r="B54" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C54" t="s">
         <v>32</v>
@@ -11782,12 +11773,12 @@
         <v>2200</v>
       </c>
       <c r="K54" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="55" spans="2:11">
       <c r="B55" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -11805,12 +11796,12 @@
         <v>65</v>
       </c>
       <c r="K55" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="56" spans="2:11">
       <c r="B56" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -11828,12 +11819,12 @@
         <v>2.6389999999999998</v>
       </c>
       <c r="K56" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="57" spans="2:11">
       <c r="B57" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -11856,7 +11847,7 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -11883,12 +11874,12 @@
         <v>40</v>
       </c>
       <c r="K58" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59" spans="2:11">
       <c r="B59" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -11915,12 +11906,12 @@
         <v>4</v>
       </c>
       <c r="K59" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="60" spans="2:11">
       <c r="B60" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -11938,12 +11929,12 @@
         <v>2300</v>
       </c>
       <c r="K60" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="61" spans="2:11">
       <c r="B61" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -11961,12 +11952,12 @@
         <v>80</v>
       </c>
       <c r="K61" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="B62" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -11989,7 +11980,7 @@
     </row>
     <row r="63" spans="2:11">
       <c r="B63" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -12016,12 +12007,12 @@
         <v>40</v>
       </c>
       <c r="K63" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" spans="2:11">
       <c r="B64" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C64" t="s">
         <v>32</v>
@@ -12048,18 +12039,18 @@
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="65" spans="2:11">
       <c r="B65" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C65" t="s">
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E65">
         <v>5500</v>
@@ -12071,18 +12062,18 @@
         <v>4500</v>
       </c>
       <c r="K65" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66" spans="2:11">
       <c r="B66" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C66" t="s">
         <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E66">
         <v>165</v>
@@ -12094,18 +12085,18 @@
         <v>135</v>
       </c>
       <c r="K66" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="67" spans="2:11">
       <c r="B67" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C67" t="s">
         <v>32</v>
       </c>
       <c r="D67" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E67">
         <v>4.4779999999999998</v>
@@ -12117,18 +12108,18 @@
         <v>3.7309999999999999</v>
       </c>
       <c r="K67" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="68" spans="2:11">
       <c r="B68" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C68" t="s">
         <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E68">
         <v>0.36</v>
@@ -12145,13 +12136,13 @@
     </row>
     <row r="69" spans="2:11">
       <c r="B69" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C69" t="s">
         <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E69">
         <v>40</v>
@@ -12172,18 +12163,18 @@
         <v>40</v>
       </c>
       <c r="K69" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="70" spans="2:11">
       <c r="B70" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C70" t="s">
         <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E70">
         <v>5</v>
@@ -12204,18 +12195,18 @@
         <v>5</v>
       </c>
       <c r="K70" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="71" spans="2:11">
       <c r="B71" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C71" t="s">
         <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E71">
         <v>5850</v>
@@ -12227,18 +12218,18 @@
         <v>5150</v>
       </c>
       <c r="K71" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="72" spans="2:11">
       <c r="B72" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C72" t="s">
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E72">
         <v>205</v>
@@ -12250,18 +12241,18 @@
         <v>180</v>
       </c>
       <c r="K72" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="73" spans="2:11">
       <c r="B73" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C73" t="s">
         <v>32</v>
       </c>
       <c r="D73" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E73">
         <v>4.5830000000000002</v>
@@ -12273,18 +12264,18 @@
         <v>4.5830000000000002</v>
       </c>
       <c r="K73" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="74" spans="2:11">
       <c r="B74" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C74" t="s">
         <v>32</v>
       </c>
       <c r="D74" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E74">
         <v>0.35</v>
@@ -12301,13 +12292,13 @@
     </row>
     <row r="75" spans="2:11">
       <c r="B75" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C75" t="s">
         <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E75">
         <v>40</v>
@@ -12328,18 +12319,18 @@
         <v>40</v>
       </c>
       <c r="K75" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="76" spans="2:11">
       <c r="B76" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E76">
         <v>5</v>
@@ -12360,18 +12351,18 @@
         <v>5</v>
       </c>
       <c r="K76" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="77" spans="2:11">
       <c r="B77" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C77" t="s">
         <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E77">
         <v>5700</v>
@@ -12383,18 +12374,18 @@
         <v>5150</v>
       </c>
       <c r="K77" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" spans="2:11">
       <c r="B78" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C78" t="s">
         <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E78">
         <v>170</v>
@@ -12406,18 +12397,18 @@
         <v>155</v>
       </c>
       <c r="K78" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="79" spans="2:11">
       <c r="B79" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C79" t="s">
         <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E79">
         <v>4.306</v>
@@ -12429,18 +12420,18 @@
         <v>4.306</v>
       </c>
       <c r="K79" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" spans="2:11">
       <c r="B80" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C80" t="s">
         <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E80">
         <v>0.36</v>
@@ -12457,13 +12448,13 @@
     </row>
     <row r="81" spans="2:11">
       <c r="B81" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C81" t="s">
         <v>32</v>
       </c>
       <c r="D81" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E81">
         <v>40</v>
@@ -12484,18 +12475,18 @@
         <v>40</v>
       </c>
       <c r="K81" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="2:11">
       <c r="B82" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C82" t="s">
         <v>32</v>
       </c>
       <c r="D82" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E82">
         <v>5</v>
@@ -12516,12 +12507,12 @@
         <v>5</v>
       </c>
       <c r="K82" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="2:11">
       <c r="B83" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C83" t="s">
         <v>36</v>
@@ -12539,12 +12530,12 @@
         <v>4500</v>
       </c>
       <c r="K83" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="84" spans="2:11">
       <c r="B84" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C84" t="s">
         <v>36</v>
@@ -12562,12 +12553,12 @@
         <v>160</v>
       </c>
       <c r="K84" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="B85" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C85" t="s">
         <v>36</v>
@@ -12582,12 +12573,12 @@
         <v>0.77800000000000002</v>
       </c>
       <c r="K85" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="86" spans="2:11">
       <c r="B86" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C86" t="s">
         <v>36</v>
@@ -12614,12 +12605,12 @@
         <v>60</v>
       </c>
       <c r="K86" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="87" spans="2:11">
       <c r="B87" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C87" t="s">
         <v>36</v>
@@ -12646,12 +12637,12 @@
         <v>7</v>
       </c>
       <c r="K87" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="B88" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C88" t="s">
         <v>36</v>
@@ -12675,12 +12666,12 @@
         <v>4884.6000000000004</v>
       </c>
       <c r="K88" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="89" spans="2:11">
       <c r="B89" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C89" t="s">
         <v>36</v>
@@ -12704,12 +12695,12 @@
         <v>136</v>
       </c>
       <c r="K89" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="90" spans="2:11">
       <c r="B90" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C90" t="s">
         <v>36</v>
@@ -12733,12 +12724,12 @@
         <v>0.72199999999999998</v>
       </c>
       <c r="K90" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="91" spans="2:11">
       <c r="B91" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C91" t="s">
         <v>36</v>
@@ -12765,12 +12756,12 @@
         <v>40</v>
       </c>
       <c r="K91" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="92" spans="2:11">
       <c r="B92" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C92" t="s">
         <v>36</v>
@@ -12797,12 +12788,12 @@
         <v>3</v>
       </c>
       <c r="K92" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="93" spans="2:11">
       <c r="B93" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
@@ -12820,12 +12811,12 @@
         <v>2300</v>
       </c>
       <c r="K93" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="94" spans="2:11">
       <c r="B94" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C94" t="s">
         <v>31</v>
@@ -12843,12 +12834,12 @@
         <v>80</v>
       </c>
       <c r="K94" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="95" spans="2:11">
       <c r="B95" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C95" t="s">
         <v>31</v>
@@ -12866,12 +12857,12 @@
         <v>1.4570000000000001</v>
       </c>
       <c r="K95" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="96" spans="2:11">
       <c r="B96" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C96" t="s">
         <v>31</v>
@@ -12894,7 +12885,7 @@
     </row>
     <row r="97" spans="2:11">
       <c r="B97" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C97" t="s">
         <v>31</v>
@@ -12912,12 +12903,12 @@
         <v>0.6</v>
       </c>
       <c r="K97" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="2:11">
       <c r="B98" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C98" t="s">
         <v>31</v>
@@ -12944,12 +12935,12 @@
         <v>45</v>
       </c>
       <c r="K98" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="99" spans="2:11">
       <c r="B99" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C99" t="s">
         <v>31</v>
@@ -12976,12 +12967,12 @@
         <v>3</v>
       </c>
       <c r="K99" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="100" spans="2:11">
       <c r="B100" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C100" t="s">
         <v>31</v>
@@ -12999,12 +12990,12 @@
         <v>575</v>
       </c>
       <c r="K100" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="101" spans="2:11">
       <c r="B101" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C101" t="s">
         <v>31</v>
@@ -13022,12 +13013,12 @@
         <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="102" spans="2:11">
       <c r="B102" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C102" t="s">
         <v>31</v>
@@ -13045,12 +13036,12 @@
         <v>1.111</v>
       </c>
       <c r="K102" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="103" spans="2:11">
       <c r="B103" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C103" t="s">
         <v>31</v>
@@ -13073,7 +13064,7 @@
     </row>
     <row r="104" spans="2:11">
       <c r="B104" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C104" t="s">
         <v>31</v>
@@ -13091,12 +13082,12 @@
         <v>0.6</v>
       </c>
       <c r="K104" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="B105" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C105" t="s">
         <v>31</v>
@@ -13123,12 +13114,12 @@
         <v>40</v>
       </c>
       <c r="K105" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="106" spans="2:11">
       <c r="B106" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C106" t="s">
         <v>31</v>
@@ -13155,18 +13146,18 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="107" spans="2:11">
       <c r="B107" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C107" t="s">
         <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E107">
         <v>3750</v>
@@ -13178,18 +13169,18 @@
         <v>3550</v>
       </c>
       <c r="K107" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="B108" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C108" t="s">
         <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E108">
         <v>140</v>
@@ -13201,18 +13192,18 @@
         <v>130</v>
       </c>
       <c r="K108" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="B109" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C109" t="s">
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E109">
         <v>1.667</v>
@@ -13224,18 +13215,18 @@
         <v>1.667</v>
       </c>
       <c r="K109" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="110" spans="2:11">
       <c r="B110" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C110" t="s">
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E110">
         <v>0.38500000000000001</v>
@@ -13252,13 +13243,13 @@
     </row>
     <row r="111" spans="2:11">
       <c r="B111" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C111" t="s">
         <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E111">
         <v>0.7</v>
@@ -13270,18 +13261,18 @@
         <v>0.7</v>
       </c>
       <c r="K111" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="B112" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E112">
         <v>25</v>
@@ -13302,18 +13293,18 @@
         <v>25</v>
       </c>
       <c r="K112" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="113" spans="2:11">
       <c r="B113" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C113" t="s">
         <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E113">
         <v>2</v>
@@ -13334,18 +13325,18 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="114" spans="2:11">
       <c r="B114" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C114" t="s">
         <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E114">
         <v>0.35389999999999999</v>
@@ -13366,18 +13357,18 @@
         <v>0.35389999999999999</v>
       </c>
       <c r="K114" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="115" spans="2:11">
       <c r="B115" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C115" t="s">
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E115">
         <v>5750</v>
@@ -13389,18 +13380,18 @@
         <v>5100</v>
       </c>
       <c r="K115" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="116" spans="2:11">
       <c r="B116" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C116" t="s">
         <v>31</v>
       </c>
       <c r="D116" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E116">
         <v>205</v>
@@ -13412,18 +13403,18 @@
         <v>180</v>
       </c>
       <c r="K116" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="117" spans="2:11">
       <c r="B117" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C117" t="s">
         <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E117">
         <v>2.3610000000000002</v>
@@ -13435,18 +13426,18 @@
         <v>2.3610000000000002</v>
       </c>
       <c r="K117" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="118" spans="2:11">
       <c r="B118" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C118" t="s">
         <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E118">
         <v>0.3</v>
@@ -13463,13 +13454,13 @@
     </row>
     <row r="119" spans="2:11">
       <c r="B119" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C119" t="s">
         <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E119">
         <v>0.6</v>
@@ -13481,18 +13472,18 @@
         <v>0.6</v>
       </c>
       <c r="K119" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="120" spans="2:11">
       <c r="B120" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C120" t="s">
         <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E120">
         <v>30</v>
@@ -13513,18 +13504,18 @@
         <v>30</v>
       </c>
       <c r="K120" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="121" spans="2:11">
       <c r="B121" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C121" t="s">
         <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E121">
         <v>3</v>
@@ -13545,12 +13536,12 @@
         <v>3</v>
       </c>
       <c r="K121" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="122" spans="2:11">
       <c r="B122" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C122" t="s">
         <v>34</v>
@@ -13568,12 +13559,12 @@
         <v>2550</v>
       </c>
       <c r="K122" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="123" spans="2:11">
       <c r="B123" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C123" t="s">
         <v>34</v>
@@ -13591,12 +13582,12 @@
         <v>50</v>
       </c>
       <c r="K123" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="124" spans="2:11">
       <c r="B124" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C124" t="s">
         <v>34</v>
@@ -13614,12 +13605,12 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="125" spans="2:11">
       <c r="B125" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C125" t="s">
         <v>34</v>
@@ -13642,7 +13633,7 @@
     </row>
     <row r="126" spans="2:11">
       <c r="B126" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C126" t="s">
         <v>34</v>
@@ -13660,12 +13651,12 @@
         <v>0.85</v>
       </c>
       <c r="K126" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="127" spans="2:11">
       <c r="B127" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C127" t="s">
         <v>34</v>
@@ -13692,12 +13683,12 @@
         <v>30</v>
       </c>
       <c r="K127" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="128" spans="2:11">
       <c r="B128" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C128" t="s">
         <v>34</v>
@@ -13724,7 +13715,7 @@
         <v>4</v>
       </c>
       <c r="K128" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C79DD69F-86F9-453E-8FBB-66ABFB5E793C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0438A14E-9DC6-4686-8F52-652A1C92D963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">conventional!$B$10:$D$128</definedName>
     <definedName name="FuelList">[1]ELC_Lists!$K$4:$K$113</definedName>
     <definedName name="HHV_Coal">[1]Costs!#REF!</definedName>
     <definedName name="HHV_H2">[1]Costs!#REF!</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="501">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1624,6 +1625,12 @@
   </si>
   <si>
     <t>e_w111615226-380_POL,e_w139452056-400_POL,e_w166838338-400_POL,e_w173613665-220_POL,e_w183945016-220_POL,e_w215282393-400_POL,e_w255277953-400_POL,e_w303870256-400_POL,e_w39428977-400_POL,e_w44389929-220_POL</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>\I: coal</t>
   </si>
 </sst>
 </file>
@@ -2127,7 +2134,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2538,6 +2545,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
@@ -10225,6 +10233,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9191BB0D-3271-4440-83E4-A7FCFCB3136A}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="21.265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:19">
       <c r="B9" t="s">
@@ -10697,7 +10708,7 @@
         <v>146</v>
       </c>
       <c r="M20" t="s">
-        <v>172</v>
+        <v>499</v>
       </c>
       <c r="N20" t="s">
         <v>485</v>
@@ -10747,7 +10758,7 @@
         <v>472</v>
       </c>
       <c r="M21" t="s">
-        <v>172</v>
+        <v>499</v>
       </c>
       <c r="N21" t="s">
         <v>486</v>
@@ -10797,7 +10808,7 @@
         <v>473</v>
       </c>
       <c r="M22" t="s">
-        <v>172</v>
+        <v>499</v>
       </c>
       <c r="N22" t="s">
         <v>487</v>
@@ -12046,8 +12057,8 @@
       <c r="B65" t="s">
         <v>485</v>
       </c>
-      <c r="C65" t="s">
-        <v>32</v>
+      <c r="C65" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D65" t="s">
         <v>480</v>
@@ -12069,8 +12080,8 @@
       <c r="B66" t="s">
         <v>485</v>
       </c>
-      <c r="C66" t="s">
-        <v>32</v>
+      <c r="C66" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D66" t="s">
         <v>480</v>
@@ -12092,8 +12103,8 @@
       <c r="B67" t="s">
         <v>485</v>
       </c>
-      <c r="C67" t="s">
-        <v>32</v>
+      <c r="C67" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D67" t="s">
         <v>480</v>
@@ -12115,8 +12126,8 @@
       <c r="B68" t="s">
         <v>485</v>
       </c>
-      <c r="C68" t="s">
-        <v>32</v>
+      <c r="C68" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D68" t="s">
         <v>480</v>
@@ -12138,8 +12149,8 @@
       <c r="B69" t="s">
         <v>485</v>
       </c>
-      <c r="C69" t="s">
-        <v>32</v>
+      <c r="C69" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D69" t="s">
         <v>480</v>
@@ -12170,8 +12181,8 @@
       <c r="B70" t="s">
         <v>485</v>
       </c>
-      <c r="C70" t="s">
-        <v>32</v>
+      <c r="C70" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D70" t="s">
         <v>480</v>
@@ -12202,8 +12213,8 @@
       <c r="B71" t="s">
         <v>486</v>
       </c>
-      <c r="C71" t="s">
-        <v>32</v>
+      <c r="C71" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D71" t="s">
         <v>480</v>
@@ -12225,8 +12236,8 @@
       <c r="B72" t="s">
         <v>486</v>
       </c>
-      <c r="C72" t="s">
-        <v>32</v>
+      <c r="C72" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D72" t="s">
         <v>480</v>
@@ -12248,8 +12259,8 @@
       <c r="B73" t="s">
         <v>486</v>
       </c>
-      <c r="C73" t="s">
-        <v>32</v>
+      <c r="C73" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D73" t="s">
         <v>480</v>
@@ -12271,8 +12282,8 @@
       <c r="B74" t="s">
         <v>486</v>
       </c>
-      <c r="C74" t="s">
-        <v>32</v>
+      <c r="C74" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D74" t="s">
         <v>480</v>
@@ -12294,8 +12305,8 @@
       <c r="B75" t="s">
         <v>486</v>
       </c>
-      <c r="C75" t="s">
-        <v>32</v>
+      <c r="C75" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D75" t="s">
         <v>480</v>
@@ -12326,8 +12337,8 @@
       <c r="B76" t="s">
         <v>486</v>
       </c>
-      <c r="C76" t="s">
-        <v>32</v>
+      <c r="C76" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D76" t="s">
         <v>480</v>
@@ -12358,8 +12369,8 @@
       <c r="B77" t="s">
         <v>487</v>
       </c>
-      <c r="C77" t="s">
-        <v>32</v>
+      <c r="C77" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D77" t="s">
         <v>480</v>
@@ -12381,8 +12392,8 @@
       <c r="B78" t="s">
         <v>487</v>
       </c>
-      <c r="C78" t="s">
-        <v>32</v>
+      <c r="C78" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D78" t="s">
         <v>480</v>
@@ -12404,8 +12415,8 @@
       <c r="B79" t="s">
         <v>487</v>
       </c>
-      <c r="C79" t="s">
-        <v>32</v>
+      <c r="C79" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D79" t="s">
         <v>480</v>
@@ -12427,8 +12438,8 @@
       <c r="B80" t="s">
         <v>487</v>
       </c>
-      <c r="C80" t="s">
-        <v>32</v>
+      <c r="C80" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D80" t="s">
         <v>480</v>
@@ -12450,8 +12461,8 @@
       <c r="B81" t="s">
         <v>487</v>
       </c>
-      <c r="C81" t="s">
-        <v>32</v>
+      <c r="C81" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D81" t="s">
         <v>480</v>
@@ -12482,8 +12493,8 @@
       <c r="B82" t="s">
         <v>487</v>
       </c>
-      <c r="C82" t="s">
-        <v>32</v>
+      <c r="C82" s="154" t="s">
+        <v>500</v>
       </c>
       <c r="D82" t="s">
         <v>480</v>
